--- a/artfynd/A 11282-2021 artfynd.xlsx
+++ b/artfynd/A 11282-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11282-2021 artfynd.xlsx
+++ b/artfynd/A 11282-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5399,10 +5399,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>111634870</v>
+        <v>111634869</v>
       </c>
       <c r="B44" t="n">
-        <v>77515</v>
+        <v>78578</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5415,21 +5415,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5442,7 +5442,7 @@
         <v>539973</v>
       </c>
       <c r="R44" t="n">
-        <v>7198378</v>
+        <v>7198379</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5511,10 +5511,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>111634869</v>
+        <v>111635413</v>
       </c>
       <c r="B45" t="n">
-        <v>78578</v>
+        <v>89369</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5523,25 +5523,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>539973</v>
+        <v>539851</v>
       </c>
       <c r="R45" t="n">
-        <v>7198379</v>
+        <v>7198362</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5611,22 +5611,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>111635413</v>
+        <v>111635499</v>
       </c>
       <c r="B46" t="n">
-        <v>89369</v>
+        <v>85715</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5635,25 +5635,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>539851</v>
+        <v>540010</v>
       </c>
       <c r="R46" t="n">
-        <v>7198362</v>
+        <v>7198354</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5735,10 +5735,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>111635499</v>
+        <v>111635462</v>
       </c>
       <c r="B47" t="n">
-        <v>85715</v>
+        <v>89590</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5747,25 +5747,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>48</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540010</v>
+        <v>539962</v>
       </c>
       <c r="R47" t="n">
-        <v>7198354</v>
+        <v>7198365</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5847,10 +5847,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>111635462</v>
+        <v>111635437</v>
       </c>
       <c r="B48" t="n">
-        <v>89590</v>
+        <v>89845</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5863,21 +5863,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>539962</v>
+        <v>539974</v>
       </c>
       <c r="R48" t="n">
-        <v>7198365</v>
+        <v>7198369</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5959,10 +5959,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>111635437</v>
+        <v>111634868</v>
       </c>
       <c r="B49" t="n">
-        <v>89845</v>
+        <v>78612</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5971,25 +5971,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5999,10 +5999,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>539974</v>
+        <v>539976</v>
       </c>
       <c r="R49" t="n">
-        <v>7198369</v>
+        <v>7198378</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6059,22 +6059,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isak Vahlström</t>
+          <t>Isak Vahlström, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>111634868</v>
+        <v>111635445</v>
       </c>
       <c r="B50" t="n">
-        <v>78612</v>
+        <v>89686</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6083,25 +6083,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>539976</v>
+        <v>539972</v>
       </c>
       <c r="R50" t="n">
-        <v>7198378</v>
+        <v>7198351</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6171,127 +6171,15 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>111635445</v>
-      </c>
-      <c r="B51" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>658</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Gäddbäcksberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>539972</v>
-      </c>
-      <c r="R51" t="n">
-        <v>7198351</v>
-      </c>
-      <c r="S51" t="n">
-        <v>25</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2023-08-22</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2023-08-22</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Yasmine Kindlund</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Yasmine Kindlund, Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
